--- a/data/trans_orig/P24D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P24D-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2007</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2007 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104458</t>
+          <t>104429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>143864</t>
+          <t>142148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43199</t>
+          <t>43432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68509</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157202</t>
+          <t>154593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201278</t>
+          <t>198159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229759</t>
+          <t>231475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269165</t>
+          <t>269194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108032</t>
+          <t>108334</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133342</t>
+          <t>133109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>348887</t>
+          <t>352006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>392963</t>
+          <t>395572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203648</t>
+          <t>206238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>259317</t>
+          <t>258282</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166941</t>
+          <t>167122</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212055</t>
+          <t>212897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>388643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>455208</t>
+          <t>456777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>557520</t>
+          <t>558555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>613189</t>
+          <t>610599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327145</t>
+          <t>326303</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372259</t>
+          <t>372078</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>900829</t>
+          <t>899260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>968100</t>
+          <t>967394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52803</t>
+          <t>52424</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80217</t>
+          <t>79163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42263</t>
+          <t>42022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64903</t>
+          <t>65719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101327</t>
+          <t>100075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135632</t>
+          <t>136331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110150</t>
+          <t>111204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>137564</t>
+          <t>137943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73831</t>
+          <t>73015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>96712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>193469</t>
+          <t>192770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227774</t>
+          <t>229026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>384310</t>
+          <t>387290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>454734</t>
+          <t>456308</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>272592</t>
+          <t>268931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>326520</t>
+          <t>323551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>671967</t>
+          <t>671062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>767700</t>
+          <t>759321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>926094</t>
+          <t>924520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>996518</t>
+          <t>993538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>527954</t>
+          <t>530923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>581882</t>
+          <t>585543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1467602</t>
+          <t>1475981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1563335</t>
+          <t>1564240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2012</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132456</t>
+          <t>134023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169200</t>
+          <t>171641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86901</t>
+          <t>86062</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115793</t>
+          <t>115787</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227623</t>
+          <t>227284</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277581</t>
+          <t>274561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165805</t>
+          <t>163364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>202549</t>
+          <t>200982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84244</t>
+          <t>84250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113136</t>
+          <t>113975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257461</t>
+          <t>260481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>307419</t>
+          <t>307758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>364730</t>
+          <t>364807</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>424796</t>
+          <t>427378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>292708</t>
+          <t>293238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>345624</t>
+          <t>345032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>676549</t>
+          <t>679597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>759121</t>
+          <t>759598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427045</t>
+          <t>424463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487111</t>
+          <t>487034</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>285907</t>
+          <t>286499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338823</t>
+          <t>338293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>724251</t>
+          <t>723774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>806823</t>
+          <t>803775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,19%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64233</t>
+          <t>62712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91264</t>
+          <t>91672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63366</t>
+          <t>63422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87834</t>
+          <t>86973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134687</t>
+          <t>135142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171498</t>
+          <t>170247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70172</t>
+          <t>69764</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97203</t>
+          <t>98724</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>50654</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74261</t>
+          <t>74205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127565</t>
+          <t>128816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164376</t>
+          <t>163921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,81%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>585836</t>
+          <t>588193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>664504</t>
+          <t>658233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>467390</t>
+          <t>463910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>530327</t>
+          <t>527689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1071491</t>
+          <t>1069082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1169276</t>
+          <t>1167296</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>683778</t>
+          <t>690049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>762446</t>
+          <t>760089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>438867</t>
+          <t>441505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>501804</t>
+          <t>505284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1148201</t>
+          <t>1150181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1245986</t>
+          <t>1248395</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,87%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2016</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2016 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79018</t>
+          <t>77905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107888</t>
+          <t>108706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49301</t>
+          <t>48890</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72221</t>
+          <t>71819</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136508</t>
+          <t>136386</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>173713</t>
+          <t>172533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116522</t>
+          <t>115704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145392</t>
+          <t>146505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63994</t>
+          <t>64396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86914</t>
+          <t>87325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186912</t>
+          <t>188092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224117</t>
+          <t>224239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,18%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>315992</t>
+          <t>313874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>374580</t>
+          <t>370473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>272132</t>
+          <t>271808</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>320161</t>
+          <t>321616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>603613</t>
+          <t>602901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>679431</t>
+          <t>680917</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430335</t>
+          <t>434442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488923</t>
+          <t>491041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340797</t>
+          <t>339342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>388826</t>
+          <t>389150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>786442</t>
+          <t>784956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>862260</t>
+          <t>862972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>51859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75545</t>
+          <t>76653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40570</t>
+          <t>40697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63015</t>
+          <t>62542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97102</t>
+          <t>97219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129990</t>
+          <t>130647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60609</t>
+          <t>59501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84342</t>
+          <t>84295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57437</t>
+          <t>57910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79882</t>
+          <t>79755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>125959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159504</t>
+          <t>159387</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>466165</t>
+          <t>464930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>536152</t>
+          <t>535211</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>377911</t>
+          <t>375578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>438411</t>
+          <t>436598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>858750</t>
+          <t>860022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>955342</t>
+          <t>953638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,78%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629326</t>
+          <t>630267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>699313</t>
+          <t>700548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>479214</t>
+          <t>481027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>539714</t>
+          <t>542047</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1127762</t>
+          <t>1129466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1224354</t>
+          <t>1223082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2023</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2023 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38589</t>
+          <t>37657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59898</t>
+          <t>60377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>33325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47117</t>
+          <t>46991</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77322</t>
+          <t>75150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103020</t>
+          <t>101761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81273</t>
+          <t>80794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102582</t>
+          <t>103514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31077</t>
+          <t>31203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44480</t>
+          <t>44869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116345</t>
+          <t>117604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142043</t>
+          <t>144215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>65,74%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168931</t>
+          <t>168054</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220393</t>
+          <t>218159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180199</t>
+          <t>180730</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217437</t>
+          <t>220998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>360945</t>
+          <t>361282</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>426154</t>
+          <t>427990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361182</t>
+          <t>363416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412644</t>
+          <t>413521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>242808</t>
+          <t>239247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>280046</t>
+          <t>279515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>615666</t>
+          <t>613830</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>680875</t>
+          <t>680538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>37165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63872</t>
+          <t>65062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>32387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50866</t>
+          <t>51347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74558</t>
+          <t>74445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109207</t>
+          <t>109161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,94%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39570</t>
+          <t>38380</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66960</t>
+          <t>66277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55878</t>
+          <t>55397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74974</t>
+          <t>74357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100979</t>
+          <t>101025</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135628</t>
+          <t>135741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,58%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>257635</t>
+          <t>260682</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>325470</t>
+          <t>325433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>258378</t>
+          <t>257873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>303260</t>
+          <t>303650</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>532738</t>
+          <t>534365</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>615432</t>
+          <t>613185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>500718</t>
+          <t>500755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>568553</t>
+          <t>565506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341924</t>
+          <t>341534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386806</t>
+          <t>387311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>855939</t>
+          <t>858186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>938633</t>
+          <t>937006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P24D-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104429</t>
+          <t>105698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142148</t>
+          <t>140856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43432</t>
+          <t>43861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68207</t>
+          <t>69188</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154593</t>
+          <t>158113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198159</t>
+          <t>199756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231475</t>
+          <t>232767</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269194</t>
+          <t>267925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108334</t>
+          <t>107353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133109</t>
+          <t>132680</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>352006</t>
+          <t>350409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>395572</t>
+          <t>392052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,26%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>206238</t>
+          <t>206982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>258282</t>
+          <t>260115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>167122</t>
+          <t>167253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212897</t>
+          <t>210009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>388643</t>
+          <t>387302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>456777</t>
+          <t>458968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>558555</t>
+          <t>556722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>610599</t>
+          <t>609855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326303</t>
+          <t>329191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372078</t>
+          <t>371947</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>899260</t>
+          <t>897069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>967394</t>
+          <t>968735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52424</t>
+          <t>53077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79163</t>
+          <t>79137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>41425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65719</t>
+          <t>63876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100075</t>
+          <t>101925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136331</t>
+          <t>136919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111204</t>
+          <t>111230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>137943</t>
+          <t>137290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73015</t>
+          <t>74858</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96712</t>
+          <t>97309</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>192770</t>
+          <t>192182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>229026</t>
+          <t>227176</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>387290</t>
+          <t>387022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>456308</t>
+          <t>457836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>268931</t>
+          <t>268296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>323551</t>
+          <t>324646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>671062</t>
+          <t>673899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>759321</t>
+          <t>762196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>924520</t>
+          <t>922992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>993538</t>
+          <t>993806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>530923</t>
+          <t>529828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>585543</t>
+          <t>586178</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1475981</t>
+          <t>1473106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1564240</t>
+          <t>1561403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134023</t>
+          <t>133373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>171641</t>
+          <t>170411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86062</t>
+          <t>86204</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115787</t>
+          <t>116649</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227284</t>
+          <t>229226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163364</t>
+          <t>164594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200982</t>
+          <t>201632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84250</t>
+          <t>83388</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113975</t>
+          <t>113833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>307758</t>
+          <t>305816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,16%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>364807</t>
+          <t>362143</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>427378</t>
+          <t>422173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>293238</t>
+          <t>296083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>345032</t>
+          <t>346120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>679597</t>
+          <t>678956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>759598</t>
+          <t>754315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424463</t>
+          <t>429668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487034</t>
+          <t>489698</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>286499</t>
+          <t>285411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338293</t>
+          <t>335448</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>723774</t>
+          <t>729057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>803775</t>
+          <t>804416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,23%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62712</t>
+          <t>64529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91672</t>
+          <t>90456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63422</t>
+          <t>64074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86973</t>
+          <t>87852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135142</t>
+          <t>133610</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170247</t>
+          <t>170530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69764</t>
+          <t>70980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98724</t>
+          <t>96907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50654</t>
+          <t>49775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74205</t>
+          <t>73553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128816</t>
+          <t>128533</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163921</t>
+          <t>165453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>588193</t>
+          <t>582382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>658233</t>
+          <t>663560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>463910</t>
+          <t>461690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>527689</t>
+          <t>528034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1069082</t>
+          <t>1069989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1167296</t>
+          <t>1170495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>690049</t>
+          <t>684722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>760089</t>
+          <t>765900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>441505</t>
+          <t>441160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>505284</t>
+          <t>507504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1150181</t>
+          <t>1146982</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1248395</t>
+          <t>1247488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77905</t>
+          <t>79198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108706</t>
+          <t>109364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48890</t>
+          <t>49480</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71819</t>
+          <t>73024</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136386</t>
+          <t>134965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172533</t>
+          <t>173107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,0%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115704</t>
+          <t>115046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146505</t>
+          <t>145212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64396</t>
+          <t>63191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87325</t>
+          <t>86735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188092</t>
+          <t>187518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224239</t>
+          <t>225660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>313874</t>
+          <t>314602</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>370473</t>
+          <t>373877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>271808</t>
+          <t>270216</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>321616</t>
+          <t>323814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>602901</t>
+          <t>600416</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>680917</t>
+          <t>679196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>434442</t>
+          <t>431038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491041</t>
+          <t>490313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339342</t>
+          <t>337144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>389150</t>
+          <t>390742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>784956</t>
+          <t>786677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>862972</t>
+          <t>865457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>59,04%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51859</t>
+          <t>50620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76653</t>
+          <t>75415</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40697</t>
+          <t>40525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62542</t>
+          <t>61908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97219</t>
+          <t>98406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130647</t>
+          <t>131051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59501</t>
+          <t>60739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84295</t>
+          <t>85534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57910</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79755</t>
+          <t>79927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125959</t>
+          <t>125555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159387</t>
+          <t>158200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>464930</t>
+          <t>468554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>535211</t>
+          <t>538390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>375578</t>
+          <t>380600</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>436598</t>
+          <t>436747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>860022</t>
+          <t>858998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>953638</t>
+          <t>955017</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>630267</t>
+          <t>627088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>700548</t>
+          <t>696924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>481027</t>
+          <t>480878</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>542047</t>
+          <t>537025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1129466</t>
+          <t>1128087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1223082</t>
+          <t>1224106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48689</t>
+          <t>51433</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37657</t>
+          <t>40952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60377</t>
+          <t>65171</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40538</t>
+          <t>45206</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>37658</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46991</t>
+          <t>52449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>89227</t>
+          <t>96639</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75150</t>
+          <t>82624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101761</t>
+          <t>112290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>101048</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80794</t>
+          <t>87310</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103514</t>
+          <t>111529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37656</t>
+          <t>40258</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31203</t>
+          <t>33015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44869</t>
+          <t>47806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>130138</t>
+          <t>141305</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117604</t>
+          <t>125654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144215</t>
+          <t>155320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>141171</t>
+          <t>152481</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141171</t>
+          <t>152481</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141171</t>
+          <t>152481</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78194</t>
+          <t>85464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78194</t>
+          <t>85464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78194</t>
+          <t>85464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>219365</t>
+          <t>237944</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>219365</t>
+          <t>237944</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>219365</t>
+          <t>237944</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>218566</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168054</t>
+          <t>190567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>218159</t>
+          <t>246099</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>199765</t>
+          <t>215078</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180730</t>
+          <t>193773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220998</t>
+          <t>235980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>393261</t>
+          <t>433644</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361282</t>
+          <t>400377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>427990</t>
+          <t>466538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>388080</t>
+          <t>412365</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363416</t>
+          <t>384832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413521</t>
+          <t>440364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>260480</t>
+          <t>282333</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>239247</t>
+          <t>261431</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>279515</t>
+          <t>303638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>648559</t>
+          <t>694698</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>613830</t>
+          <t>661804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>680538</t>
+          <t>727965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>581575</t>
+          <t>630931</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>581575</t>
+          <t>630931</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>581575</t>
+          <t>630931</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>460245</t>
+          <t>497411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>460245</t>
+          <t>497411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>460245</t>
+          <t>497411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1041820</t>
+          <t>1128342</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1041820</t>
+          <t>1128342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1041820</t>
+          <t>1128342</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48489</t>
+          <t>49165</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65062</t>
+          <t>60712</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40770</t>
+          <t>46024</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32387</t>
+          <t>36717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51347</t>
+          <t>56314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89259</t>
+          <t>95189</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74445</t>
+          <t>81179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109161</t>
+          <t>110188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54953</t>
+          <t>61117</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38380</t>
+          <t>49570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66277</t>
+          <t>71396</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65974</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55397</t>
+          <t>60366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74357</t>
+          <t>79963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>120927</t>
+          <t>131773</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101025</t>
+          <t>116774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135741</t>
+          <t>145783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,23%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>110282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>110282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>110282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>106744</t>
+          <t>116680</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106744</t>
+          <t>116680</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106744</t>
+          <t>116680</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>210186</t>
+          <t>226962</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>210186</t>
+          <t>226962</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>210186</t>
+          <t>226962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>290674</t>
+          <t>319164</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>260682</t>
+          <t>287572</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>325433</t>
+          <t>351293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>281073</t>
+          <t>306308</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>257873</t>
+          <t>283969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>303650</t>
+          <t>331403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>571747</t>
+          <t>625472</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>534365</t>
+          <t>586559</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>613185</t>
+          <t>665603</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>535514</t>
+          <t>574529</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>500755</t>
+          <t>542400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>565506</t>
+          <t>606121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>364111</t>
+          <t>393247</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341534</t>
+          <t>368152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387311</t>
+          <t>415586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>899624</t>
+          <t>967776</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>858186</t>
+          <t>927645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>937006</t>
+          <t>1006689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>826188</t>
+          <t>893693</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>826188</t>
+          <t>893693</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>826188</t>
+          <t>893693</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>645184</t>
+          <t>699555</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>645184</t>
+          <t>699555</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>645184</t>
+          <t>699555</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1471371</t>
+          <t>1593248</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1471371</t>
+          <t>1593248</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1471371</t>
+          <t>1593248</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
